--- a/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
+++ b/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I58" s="2"/>
@@ -3199,12 +3199,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無·</t>
+          <t xml:space="preserve">–|無·</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無·</t>
         </is>
       </c>
@@ -3313,12 +3313,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3541,12 +3541,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I79" s="2"/>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無·</t>
+          <t xml:space="preserve">–|無·</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無·</t>
         </is>
       </c>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E8" s="10"/>
@@ -4919,7 +4919,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無·</t>
         </is>
       </c>
@@ -4928,14 +4928,14 @@
       <c r="E11" s="10"/>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無·</t>
         </is>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="10"/>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="N14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
+++ b/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4238,109 +4276,109 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">제주도 타령 / 담바귀 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">낮에</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4348,79 +4386,79 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">해나</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">바귀</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">낮에</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">녁</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">침</t>
         </is>
@@ -4428,78 +4466,78 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無·</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">작</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="24"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4507,78 +4545,78 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">밤에</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우는</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우는</t>
         </is>
@@ -4586,79 +4624,79 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">령</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">밤에</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="23"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4666,76 +4704,76 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="E8" s="24"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="24"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">냐</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4743,86 +4781,86 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">참사</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">두리</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">배가</t>
         </is>
@@ -4830,86 +4868,86 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">작</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">작</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">랑이</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">그리</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고파</t>
         </is>
@@ -4917,147 +4955,147 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無·</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無·</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="24"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="24"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="Q11" s="10"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -5065,76 +5103,76 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="Q13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5142,69 +5180,69 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="24"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="24"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="24"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>

--- a/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
+++ b/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
@@ -4253,28 +4253,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無·</t>
+          <t xml:space="preserve">無–</t>
         </is>
       </c>
       <c r="I5" s="24" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -4543,11 +4543,11 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="22"/>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G6" s="22"/>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4953,12 +4953,12 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-無·</t>
+無–</t>
         </is>
       </c>
       <c r="C11" s="24"/>
@@ -4967,7 +4967,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-無·</t>
+無–</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>

--- a/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
+++ b/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
@@ -4347,7 +4347,8 @@
       </c>
       <c r="K3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">낮에</t>
+          <t xml:space="preserve">낮
+에</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
@@ -4394,7 +4395,8 @@
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">해나</t>
+          <t xml:space="preserve">해
+나</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -4412,7 +4414,8 @@
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">바귀</t>
+          <t xml:space="preserve">바
+귀</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
@@ -4430,7 +4433,8 @@
       </c>
       <c r="K4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">낮에</t>
+          <t xml:space="preserve">낮
+에</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
@@ -4585,7 +4589,8 @@
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">밤에</t>
+          <t xml:space="preserve">밤
+에</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -4607,7 +4612,8 @@
       </c>
       <c r="O6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우는</t>
+          <t xml:space="preserve">우
+는</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
@@ -4618,7 +4624,8 @@
       </c>
       <c r="Q6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우는</t>
+          <t xml:space="preserve">우
+는</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4679,8 @@
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">밤에</t>
+          <t xml:space="preserve">밤
+에</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -4829,7 +4837,8 @@
       </c>
       <c r="K9" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">참사</t>
+          <t xml:space="preserve">참
+사</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -4840,7 +4849,8 @@
       </c>
       <c r="M9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">두리</t>
+          <t xml:space="preserve">두
+리</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -4862,7 +4872,8 @@
       </c>
       <c r="Q9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">배가</t>
+          <t xml:space="preserve">배
+가</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4927,8 @@
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑이</t>
+          <t xml:space="preserve">랑
+이</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -4938,7 +4950,8 @@
       </c>
       <c r="O10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">그리</t>
+          <t xml:space="preserve">그
+리</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
@@ -4949,7 +4962,8 @@
       </c>
       <c r="Q10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">고파</t>
+          <t xml:space="preserve">고
+파</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
+++ b/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +238,21 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4304,7 +4324,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4314,7 +4334,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
@@ -4324,7 +4344,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
@@ -4334,7 +4354,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -4345,7 +4365,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">낮
 에</t>
@@ -4357,7 +4377,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4368,7 +4388,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4379,7 +4399,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4393,7 +4413,7 @@
 南</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">해
 나</t>
@@ -4405,14 +4425,14 @@
 汰</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">바
 귀</t>
@@ -4424,14 +4444,14 @@
 汰</t>
         </is>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="29"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">낮
 에</t>
@@ -4442,7 +4462,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="M4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4452,7 +4472,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O4" s="23" t="inlineStr">
+      <c r="O4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">녁</t>
         </is>
@@ -4462,7 +4482,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q4" s="23" t="inlineStr">
+      <c r="Q4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">침</t>
         </is>
@@ -4475,7 +4495,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -4485,7 +4505,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
@@ -4495,7 +4515,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
@@ -4505,7 +4525,7 @@
           <t xml:space="preserve">無–</t>
         </is>
       </c>
-      <c r="I5" s="24" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">작</t>
         </is>
@@ -4515,7 +4535,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K5" s="24" t="inlineStr">
+      <c r="K5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4525,13 +4545,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="24"/>
+      <c r="M5" s="30"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="O5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4541,7 +4561,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q5" s="24" t="inlineStr">
+      <c r="Q5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4554,13 +4574,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
@@ -4570,13 +4590,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="28"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -4587,7 +4607,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">밤
 에</t>
@@ -4599,7 +4619,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4610,7 +4630,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 는</t>
@@ -4622,7 +4642,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 는</t>
@@ -4636,7 +4656,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -4646,7 +4666,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -4656,7 +4676,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">령</t>
         </is>
@@ -4666,7 +4686,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4677,7 +4697,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">밤
 에</t>
@@ -4688,13 +4708,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M7" s="23"/>
+      <c r="M7" s="29"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O7" s="23" t="inlineStr">
+      <c r="O7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4704,7 +4724,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="23" t="inlineStr">
+      <c r="Q7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4717,7 +4737,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4727,13 +4747,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="24"/>
+      <c r="E8" s="30"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4743,13 +4763,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="24"/>
+      <c r="I8" s="30"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="24" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4760,7 +4780,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M8" s="24" t="inlineStr">
+      <c r="M8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">냐</t>
         </is>
@@ -4770,7 +4790,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="O8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4781,7 +4801,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q8" s="24" t="inlineStr">
+      <c r="Q8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4794,7 +4814,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
@@ -4804,7 +4824,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
@@ -4814,7 +4834,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -4824,7 +4844,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -4835,7 +4855,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">참
 사</t>
@@ -4847,7 +4867,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">두
 리</t>
@@ -4859,7 +4879,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -4870,7 +4890,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">배
 가</t>
@@ -4884,7 +4904,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
@@ -4894,7 +4914,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
@@ -4904,7 +4924,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">작</t>
         </is>
@@ -4914,7 +4934,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">작</t>
         </is>
@@ -4925,7 +4945,7 @@
 南</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑
 이</t>
@@ -4937,7 +4957,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr">
+      <c r="M10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
@@ -4948,7 +4968,7 @@
 南</t>
         </is>
       </c>
-      <c r="O10" s="23" t="inlineStr">
+      <c r="O10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 리</t>
@@ -4960,7 +4980,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q10" s="23" t="inlineStr">
+      <c r="Q10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">고
 파</t>
@@ -4975,29 +4995,29 @@
 無–</t>
         </is>
       </c>
-      <c r="C11" s="24"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="21"/>
-      <c r="E11" s="24"/>
+      <c r="E11" s="30"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無–</t>
         </is>
       </c>
-      <c r="G11" s="24"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="24"/>
+      <c r="I11" s="30"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="24" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -5008,7 +5028,7 @@
 湳</t>
         </is>
       </c>
-      <c r="M11" s="24" t="inlineStr">
+      <c r="M11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -5019,7 +5039,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="O11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
@@ -5030,7 +5050,7 @@
 湳</t>
         </is>
       </c>
-      <c r="Q11" s="24"/>
+      <c r="Q11" s="30"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -5039,7 +5059,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
@@ -5049,7 +5069,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
@@ -5059,7 +5079,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -5069,7 +5089,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -5079,7 +5099,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5089,7 +5109,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
@@ -5099,7 +5119,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5109,7 +5129,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -5122,7 +5142,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5132,13 +5152,13 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -5148,13 +5168,13 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="29"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5165,7 +5185,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
+      <c r="M13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5175,7 +5195,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O13" s="23" t="inlineStr">
+      <c r="O13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5186,7 +5206,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q13" s="23" t="inlineStr">
+      <c r="Q13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5199,13 +5219,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5216,13 +5236,13 @@
 △</t>
         </is>
       </c>
-      <c r="G14" s="24"/>
+      <c r="G14" s="30"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -5233,13 +5253,13 @@
 △</t>
         </is>
       </c>
-      <c r="K14" s="24"/>
+      <c r="K14" s="30"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="24" t="inlineStr">
+      <c r="M14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -5250,13 +5270,13 @@
 △</t>
         </is>
       </c>
-      <c r="O14" s="24"/>
+      <c r="O14" s="30"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q14" s="24" t="inlineStr">
+      <c r="Q14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>

--- a/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
+++ b/sheets/민요/검수/제주도 타령 담바귀 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,25 +227,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -359,7 +339,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
@@ -423,7 +403,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인쇄된 12정간 양식(줄 번호 1~8, 정간 번호 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 위 괄호 "제주도 타령 중모리", 5~8줄 위 괄호 "담바귀 타령 굿거리". 오른쪽 여백에 "제주도 타령 &lt;중모리&gt; △ 담바위 타령 &lt;굿거리&gt;". 아래 여백 메모 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 각 율명 줄 바로 오른쪽 좁은 칸의 가사를 전사함. 古처럼 흘린 글자 중 女변이 없는 것은 南, 있는 것은 姑로 적음. 2_제주도 타령 닐리리야와 같은 제주도 타령 가락. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 1~8, 정간 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 "제주도 타령 중모리", 5~8줄 "담바귀 타령 굿거리"(오른쪽 여백에도 같은 표기). 아래 여백 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 1줄 9·7줄 2·8줄 9 가사 칸의 ㅣ(늘임 표시)는 생략. 女변 있는 흘림은 姑, 없는 것은 南.</t>
         </is>
       </c>
     </row>
@@ -3025,22 +3005,26 @@
       <c r="F64" s="2">
         <v>1</v>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
       </c>
-      <c r="J64" s="4"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아랫부분이 黃처럼 보임, 8줄 3과 같은 가락이라 無</t>
+        </is>
+      </c>
       <c r="K64" s="2"/>
     </row>
     <row r="65">
@@ -4294,7 +4278,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4317,14 +4301,14 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4334,7 +4318,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
@@ -4344,7 +4328,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="28" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
@@ -4354,7 +4338,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -4365,7 +4349,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">낮
 에</t>
@@ -4377,7 +4361,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M3" s="28" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4388,7 +4372,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="O3" s="28" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4399,13 +4383,13 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q3" s="28" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4413,7 +4397,7 @@
 南</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">해
 나</t>
@@ -4425,14 +4409,14 @@
 汰</t>
         </is>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">바
 귀</t>
@@ -4444,14 +4428,14 @@
 汰</t>
         </is>
       </c>
-      <c r="I4" s="29"/>
+      <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K4" s="29" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">낮
 에</t>
@@ -4462,7 +4446,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M4" s="29" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4472,7 +4456,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O4" s="29" t="inlineStr">
+      <c r="O4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">녁</t>
         </is>
@@ -4482,20 +4466,20 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q4" s="29" t="inlineStr">
+      <c r="Q4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">침</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="55.19" customHeight="1">
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -4505,17 +4489,17 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G5" s="30" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
@@ -4525,7 +4509,7 @@
           <t xml:space="preserve">無–</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
+      <c r="I5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">작</t>
         </is>
@@ -4535,7 +4519,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K5" s="30" t="inlineStr">
+      <c r="K5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4545,13 +4529,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="30"/>
+      <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O5" s="30" t="inlineStr">
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4561,26 +4545,26 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q5" s="30" t="inlineStr">
+      <c r="Q5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="55.19" customHeight="1">
+    <row r="6" ht="52.21" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="28"/>
+      <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
@@ -4590,13 +4574,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="28"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -4607,7 +4591,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">밤
 에</t>
@@ -4619,7 +4603,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M6" s="28" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4630,7 +4614,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="O6" s="28" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 는</t>
@@ -4642,21 +4626,21 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q6" s="28" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 는</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="55.19" customHeight="1">
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -4666,7 +4650,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -4676,7 +4660,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">령</t>
         </is>
@@ -4686,7 +4670,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4697,7 +4681,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K7" s="29" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">밤
 에</t>
@@ -4708,13 +4692,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M7" s="29"/>
+      <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O7" s="29" t="inlineStr">
+      <c r="O7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4724,20 +4708,20 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="29" t="inlineStr">
+      <c r="Q7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="55.19" customHeight="1">
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4747,13 +4731,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="30"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4763,13 +4747,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="30"/>
+      <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="K8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4780,7 +4764,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M8" s="30" t="inlineStr">
+      <c r="M8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">냐</t>
         </is>
@@ -4790,7 +4774,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="30" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4801,20 +4785,20 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q8" s="30" t="inlineStr">
+      <c r="Q8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="55.19" customHeight="1">
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
@@ -4824,7 +4808,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
@@ -4834,7 +4818,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -4844,7 +4828,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -4855,7 +4839,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K9" s="31" t="inlineStr">
+      <c r="K9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">참
 사</t>
@@ -4867,7 +4851,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M9" s="28" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">두
 리</t>
@@ -4879,7 +4863,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O9" s="28" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -4890,21 +4874,21 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q9" s="28" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">배
 가</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="55.19" customHeight="1">
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
@@ -4914,7 +4898,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
@@ -4924,7 +4908,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G10" s="29" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">작</t>
         </is>
@@ -4934,7 +4918,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I10" s="29" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">작</t>
         </is>
@@ -4945,7 +4929,7 @@
 南</t>
         </is>
       </c>
-      <c r="K10" s="29" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">랑
 이</t>
@@ -4957,7 +4941,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M10" s="29" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
@@ -4968,7 +4952,7 @@
 南</t>
         </is>
       </c>
-      <c r="O10" s="29" t="inlineStr">
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 리</t>
@@ -4980,14 +4964,14 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q10" s="29" t="inlineStr">
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고
 파</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="55.19" customHeight="1">
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4995,29 +4979,29 @@
 無–</t>
         </is>
       </c>
-      <c r="C11" s="30"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="21"/>
-      <c r="E11" s="30"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無–</t>
         </is>
       </c>
-      <c r="G11" s="30"/>
+      <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="30"/>
+      <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="30" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -5028,7 +5012,7 @@
 湳</t>
         </is>
       </c>
-      <c r="M11" s="30" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -5039,7 +5023,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O11" s="30" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
@@ -5050,16 +5034,16 @@
 湳</t>
         </is>
       </c>
-      <c r="Q11" s="30"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+      <c r="Q11" s="24"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
@@ -5069,7 +5053,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
@@ -5079,7 +5063,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -5089,7 +5073,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -5099,7 +5083,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="28" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5109,7 +5093,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="28" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
@@ -5119,7 +5103,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="28" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5129,20 +5113,20 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q12" s="28" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="55.19" customHeight="1">
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5152,13 +5136,13 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E13" s="29"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="29" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -5168,13 +5152,13 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I13" s="29"/>
+      <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="29" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5185,7 +5169,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M13" s="29" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5195,7 +5179,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O13" s="29" t="inlineStr">
+      <c r="O13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5206,26 +5190,26 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q13" s="29" t="inlineStr">
+      <c r="Q13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="55.19" customHeight="1">
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="32"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5236,13 +5220,13 @@
 △</t>
         </is>
       </c>
-      <c r="G14" s="30"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I14" s="30" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -5253,13 +5237,13 @@
 △</t>
         </is>
       </c>
-      <c r="K14" s="30"/>
+      <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="30" t="inlineStr">
+      <c r="M14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -5270,13 +5254,13 @@
 △</t>
         </is>
       </c>
-      <c r="O14" s="30"/>
+      <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q14" s="30" t="inlineStr">
+      <c r="Q14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
